--- a/data/trans_dic/MCS12_SP_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,54; 47,7</t>
+          <t>36,0; 47,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50,46; 61,37</t>
+          <t>49,7; 62,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49,97; 62,21</t>
+          <t>50,19; 62,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,57; 40,81</t>
+          <t>27,31; 39,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,33; 58,83</t>
+          <t>45,49; 58,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,0; 79,74</t>
+          <t>68,95; 79,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,92; 72,89</t>
+          <t>62,0; 73,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,22; 40,93</t>
+          <t>30,76; 40,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42,53; 51,11</t>
+          <t>42,28; 51,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61,18; 69,23</t>
+          <t>60,84; 69,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,86; 66,2</t>
+          <t>57,78; 65,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,85; 39,34</t>
+          <t>30,81; 38,98</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>51,35; 60,58</t>
+          <t>51,09; 60,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,68; 29,66</t>
+          <t>21,4; 29,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,73; 25,36</t>
+          <t>17,91; 25,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,93; 32,51</t>
+          <t>22,67; 33,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,87; 72,21</t>
+          <t>63,62; 72,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,26; 46,35</t>
+          <t>37,3; 45,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,76; 33,21</t>
+          <t>25,16; 33,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,07; 41,59</t>
+          <t>33,95; 41,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,89; 65,04</t>
+          <t>58,76; 65,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,21; 36,56</t>
+          <t>30,69; 36,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,57; 28,05</t>
+          <t>22,36; 27,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,63; 36,16</t>
+          <t>29,63; 36,12</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,28; 32,25</t>
+          <t>21,7; 32,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,57; 54,97</t>
+          <t>43,22; 54,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,74; 54,8</t>
+          <t>43,63; 54,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,03; 32,05</t>
+          <t>22,48; 31,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,68; 46,96</t>
+          <t>35,3; 46,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,78; 71,67</t>
+          <t>60,74; 71,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,72; 67,07</t>
+          <t>55,7; 66,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,25; 42,2</t>
+          <t>33,07; 41,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,9; 37,87</t>
+          <t>30,5; 37,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,92; 61,76</t>
+          <t>53,83; 61,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,36; 58,8</t>
+          <t>51,33; 58,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,31; 35,29</t>
+          <t>29,22; 35,63</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,35; 46,99</t>
+          <t>36,2; 46,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,86; 69,22</t>
+          <t>58,9; 69,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,34; 49,81</t>
+          <t>38,76; 49,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,03; 39,19</t>
+          <t>26,37; 39,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,05; 55,43</t>
+          <t>45,44; 55,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,1; 79,38</t>
+          <t>70,32; 79,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,05; 59,4</t>
+          <t>49,02; 59,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,94; 66,35</t>
+          <t>34,95; 66,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,75; 49,9</t>
+          <t>42,43; 49,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66,3; 73,09</t>
+          <t>66,32; 72,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,46; 52,8</t>
+          <t>45,5; 53,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>33,86; 57,71</t>
+          <t>34,11; 58,88</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>41,2; 54,84</t>
+          <t>40,51; 54,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,49; 43,41</t>
+          <t>29,73; 42,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81,72; 90,76</t>
+          <t>82,07; 90,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70,39; 81,31</t>
+          <t>70,43; 81,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>52,96; 66,22</t>
+          <t>53,29; 66,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,83; 57,32</t>
+          <t>43,74; 57,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,0; 91,93</t>
+          <t>82,94; 91,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,52; 87,09</t>
+          <t>79,06; 86,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48,84; 58,94</t>
+          <t>49,31; 58,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,68; 48,97</t>
+          <t>38,33; 48,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84,05; 89,98</t>
+          <t>83,66; 89,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,46; 83,15</t>
+          <t>76,54; 83,53</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,49; 39,74</t>
+          <t>28,87; 40,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48,23; 60,77</t>
+          <t>47,48; 60,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,68; 41,7</t>
+          <t>29,04; 40,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,21; 39,82</t>
+          <t>29,2; 39,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,55; 53,21</t>
+          <t>40,62; 52,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57,59; 69,3</t>
+          <t>57,7; 69,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,38; 51,17</t>
+          <t>39,79; 51,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33,44; 42,36</t>
+          <t>32,74; 42,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,34; 44,22</t>
+          <t>36,55; 44,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54,19; 62,56</t>
+          <t>54,27; 63,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36,04; 44,66</t>
+          <t>36,3; 44,73</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,31; 39,42</t>
+          <t>32,71; 39,77</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,1; 38,93</t>
+          <t>31,49; 39,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,03; 59,06</t>
+          <t>51,13; 59,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48,62; 56,72</t>
+          <t>49,14; 57,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,43; 57,63</t>
+          <t>47,39; 57,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,07; 52,97</t>
+          <t>45,08; 52,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,26; 68,79</t>
+          <t>61,58; 69,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,47; 61,36</t>
+          <t>53,41; 61,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,05; 88,88</t>
+          <t>62,09; 86,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39,36; 44,86</t>
+          <t>39,38; 44,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,96; 63,43</t>
+          <t>57,43; 63,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52,65; 58,21</t>
+          <t>52,52; 58,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,88; 77,75</t>
+          <t>57,09; 78,84</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>48,43; 55,42</t>
+          <t>48,77; 56,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47,25; 54,52</t>
+          <t>46,66; 54,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50,77; 57,91</t>
+          <t>50,13; 57,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,52; 51,97</t>
+          <t>16,52; 51,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,9; 62,17</t>
+          <t>54,76; 61,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,32; 65,35</t>
+          <t>58,52; 65,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,05; 60,23</t>
+          <t>53,14; 60,5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,61; 63,23</t>
+          <t>56,97; 63,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52,77; 58,06</t>
+          <t>52,68; 57,84</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53,95; 59,04</t>
+          <t>53,65; 58,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52,72; 57,78</t>
+          <t>52,76; 58,05</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,24; 56,36</t>
+          <t>27,26; 56,01</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41,41; 44,98</t>
+          <t>41,49; 45,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47,28; 50,73</t>
+          <t>47,31; 50,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46,4; 49,84</t>
+          <t>46,51; 50,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28,37; 42,04</t>
+          <t>30,56; 42,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52,47; 55,94</t>
+          <t>52,4; 56,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60,19; 63,49</t>
+          <t>60,17; 63,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,1; 56,57</t>
+          <t>53,18; 56,77</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50,04; 61,56</t>
+          <t>50,15; 62,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47,59; 50,01</t>
+          <t>47,47; 49,9</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54,27; 56,69</t>
+          <t>54,39; 56,82</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50,42; 52,82</t>
+          <t>50,21; 52,73</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41,95; 50,83</t>
+          <t>41,94; 51,27</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población por debajo de la mediana (53.579) de la puntuación del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97033; 130222</t>
+          <t>98287; 128564</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148710; 180885</t>
+          <t>146499; 182932</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>146787; 182744</t>
+          <t>147435; 182943</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85858; 127112</t>
+          <t>85062; 124230</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>120850; 153438</t>
+          <t>118650; 153441</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>198189; 229042</t>
+          <t>198065; 229456</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>178758; 210427</t>
+          <t>179010; 211294</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90431; 118560</t>
+          <t>89080; 117901</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>227049; 272842</t>
+          <t>225734; 273363</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>356042; 402925</t>
+          <t>354103; 402159</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>337028; 385593</t>
+          <t>336543; 381315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>185404; 236448</t>
+          <t>185162; 234319</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>253213; 298697</t>
+          <t>251902; 296146</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>109620; 149953</t>
+          <t>108206; 150558</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89082; 127440</t>
+          <t>89998; 126215</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>118648; 168251</t>
+          <t>117298; 171214</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>321851; 363890</t>
+          <t>320626; 364253</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>195147; 242767</t>
+          <t>195345; 240743</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>129533; 173698</t>
+          <t>131606; 174526</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>174952; 213600</t>
+          <t>174341; 215320</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>587179; 648459</t>
+          <t>585875; 648448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>310984; 376262</t>
+          <t>315881; 379294</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>231534; 287688</t>
+          <t>229320; 285717</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>305562; 372878</t>
+          <t>305548; 372395</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71028; 102836</t>
+          <t>69188; 103449</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>141181; 178139</t>
+          <t>140067; 177119</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139338; 174585</t>
+          <t>139000; 173422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69201; 100647</t>
+          <t>70612; 99957</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>119670; 157517</t>
+          <t>118394; 155407</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>207288; 244412</t>
+          <t>207125; 244189</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>187390; 225569</t>
+          <t>187338; 222503</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>114426; 145209</t>
+          <t>113783; 144472</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>202168; 247787</t>
+          <t>199572; 248076</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>358570; 410738</t>
+          <t>357979; 409743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>336351; 385057</t>
+          <t>336164; 385729</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>192899; 232245</t>
+          <t>192313; 234516</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>130378; 168549</t>
+          <t>129829; 167361</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>220124; 258877</t>
+          <t>220272; 259383</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>145536; 184297</t>
+          <t>143414; 182822</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79694; 120000</t>
+          <t>80733; 120029</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>167325; 205884</t>
+          <t>168786; 205756</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>272648; 308735</t>
+          <t>273504; 307641</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>189955; 230051</t>
+          <t>189842; 231103</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>169082; 312186</t>
+          <t>164430; 314072</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>312157; 364356</t>
+          <t>309828; 362832</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>505850; 557657</t>
+          <t>506012; 555130</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>344226; 399798</t>
+          <t>344531; 402183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>262976; 448241</t>
+          <t>264951; 457321</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>83772; 111496</t>
+          <t>82367; 111106</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>62711; 92290</t>
+          <t>63217; 91340</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172619; 191698</t>
+          <t>173351; 191828</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125461; 144929</t>
+          <t>125531; 145966</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>109985; 137513</t>
+          <t>110669; 139053</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96254; 125863</t>
+          <t>96054; 126520</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>181433; 200952</t>
+          <t>181304; 200115</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>164323; 179969</t>
+          <t>163381; 179497</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>200728; 242212</t>
+          <t>202639; 242280</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>167175; 211635</t>
+          <t>165646; 209189</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>361252; 386744</t>
+          <t>359584; 386022</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>294278; 320025</t>
+          <t>294601; 321481</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>77160; 107618</t>
+          <t>78172; 109732</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>132128; 166504</t>
+          <t>130088; 165772</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78103; 109735</t>
+          <t>76410; 107505</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78616; 107179</t>
+          <t>78591; 106841</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>112775; 148014</t>
+          <t>112979; 145455</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>161274; 194071</t>
+          <t>161569; 195322</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>107565; 139740</t>
+          <t>108670; 141912</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>85971; 108900</t>
+          <t>84162; 109593</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>199491; 242750</t>
+          <t>200634; 246048</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>300246; 346569</t>
+          <t>300652; 349178</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>193258; 239510</t>
+          <t>194637; 239882</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>170028; 207434</t>
+          <t>172123; 209295</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>191279; 239433</t>
+          <t>193679; 239938</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>338201; 391440</t>
+          <t>338897; 394137</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>319200; 372401</t>
+          <t>322642; 376137</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>293994; 357228</t>
+          <t>293769; 355192</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>287657; 338077</t>
+          <t>287707; 336946</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>425048; 477333</t>
+          <t>427250; 479121</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>369664; 424183</t>
+          <t>369187; 422823</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>525494; 752701</t>
+          <t>525784; 734326</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>493250; 562246</t>
+          <t>493496; 560623</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>786325; 860465</t>
+          <t>779124; 857495</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>709595; 784534</t>
+          <t>707831; 782686</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>834341; 1140452</t>
+          <t>837413; 1156375</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>360191; 412225</t>
+          <t>362728; 417942</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>368126; 424735</t>
+          <t>363522; 422891</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>395286; 450899</t>
+          <t>390290; 447412</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>153188; 481867</t>
+          <t>153185; 480900</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>430139; 487109</t>
+          <t>429087; 485345</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>480493; 538355</t>
+          <t>482148; 537852</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>438268; 497576</t>
+          <t>439059; 499797</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>404927; 452266</t>
+          <t>407438; 452295</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>805900; 886728</t>
+          <t>804644; 883420</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>864740; 946381</t>
+          <t>859911; 945633</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>846023; 927260</t>
+          <t>846689; 931619</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>480241; 925618</t>
+          <t>447793; 919980</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1356877; 1473889</t>
+          <t>1359326; 1474346</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1620190; 1738378</t>
+          <t>1621155; 1735304</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1575082; 1691855</t>
+          <t>1578751; 1701411</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>976902; 1447636</t>
+          <t>1052445; 1456307</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1773088; 1890301</t>
+          <t>1770768; 1893868</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2141823; 2259257</t>
+          <t>2141157; 2255406</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1882208; 2005086</t>
+          <t>1884984; 2012236</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1823309; 2243155</t>
+          <t>1827309; 2268094</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3167492; 3328852</t>
+          <t>3159395; 3321312</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3790831; 3959656</t>
+          <t>3799360; 3968661</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3498469; 3664912</t>
+          <t>3483912; 3659063</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2972898; 3602461</t>
+          <t>2972143; 3633796</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/MCS12_SP_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/MCS12_SP_R2-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,0; 47,09</t>
+          <t>34,79; 46,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49,7; 62,07</t>
+          <t>50,35; 62,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50,19; 62,28</t>
+          <t>49,6; 61,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,31; 39,89</t>
+          <t>28,21; 39,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>45,49; 58,83</t>
+          <t>46,17; 58,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,95; 79,88</t>
+          <t>68,64; 79,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,0; 73,19</t>
+          <t>61,14; 72,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,76; 40,71</t>
+          <t>30,83; 40,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>42,28; 51,21</t>
+          <t>41,51; 50,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60,84; 69,1</t>
+          <t>61,04; 69,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,78; 65,47</t>
+          <t>57,29; 66,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,81; 38,98</t>
+          <t>30,81; 37,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>51,09; 60,06</t>
+          <t>51,48; 60,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,4; 29,78</t>
+          <t>21,38; 29,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 25,11</t>
+          <t>17,61; 25,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 33,08</t>
+          <t>23,13; 33,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,62; 72,28</t>
+          <t>64,4; 72,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,3; 45,96</t>
+          <t>36,66; 46,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,16; 33,36</t>
+          <t>25,3; 32,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,95; 41,93</t>
+          <t>34,2; 41,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,76; 65,04</t>
+          <t>58,73; 64,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30,69; 36,85</t>
+          <t>30,65; 36,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,36; 27,86</t>
+          <t>22,51; 28,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>29,63; 36,12</t>
+          <t>29,54; 35,89</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,7; 32,44</t>
+          <t>22,17; 32,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,22; 54,66</t>
+          <t>43,1; 54,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,63; 54,44</t>
+          <t>43,35; 54,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,48; 31,83</t>
+          <t>23,38; 32,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,3; 46,33</t>
+          <t>35,75; 46,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,74; 71,61</t>
+          <t>61,03; 71,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,7; 66,16</t>
+          <t>55,74; 66,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>33,07; 41,98</t>
+          <t>33,44; 42,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,5; 37,92</t>
+          <t>30,48; 37,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,83; 61,61</t>
+          <t>53,98; 61,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,33; 58,9</t>
+          <t>51,2; 59,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,22; 35,63</t>
+          <t>30,29; 36,56</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>36,81%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,2; 46,66</t>
+          <t>36,57; 46,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,9; 69,36</t>
+          <t>58,78; 69,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,76; 49,42</t>
+          <t>39,1; 49,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,37; 39,2</t>
+          <t>25,81; 37,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,44; 55,39</t>
+          <t>45,67; 55,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,32; 79,1</t>
+          <t>69,83; 79,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,02; 59,67</t>
+          <t>48,62; 58,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,95; 66,76</t>
+          <t>36,39; 46,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,43; 49,69</t>
+          <t>42,76; 49,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66,32; 72,76</t>
+          <t>65,66; 73,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45,5; 53,11</t>
+          <t>45,58; 53,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>34,11; 58,88</t>
+          <t>33,12; 40,63</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,51; 54,65</t>
+          <t>41,49; 55,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,73; 42,96</t>
+          <t>30,25; 43,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,07; 90,82</t>
+          <t>81,8; 90,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70,43; 81,89</t>
+          <t>68,59; 80,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,29; 66,96</t>
+          <t>53,44; 66,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,74; 57,62</t>
+          <t>44,11; 56,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,94; 91,55</t>
+          <t>83,28; 91,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>79,06; 86,86</t>
+          <t>78,64; 86,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>49,31; 58,95</t>
+          <t>48,73; 59,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38,33; 48,4</t>
+          <t>39,13; 48,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83,66; 89,81</t>
+          <t>84,08; 90,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,54; 83,53</t>
+          <t>75,4; 82,56</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,87; 40,52</t>
+          <t>28,98; 40,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,48; 60,51</t>
+          <t>48,33; 59,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,04; 40,86</t>
+          <t>28,77; 40,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29,2; 39,69</t>
+          <t>28,77; 38,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,62; 52,29</t>
+          <t>39,96; 52,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>57,7; 69,75</t>
+          <t>57,55; 68,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>39,79; 51,96</t>
+          <t>39,39; 52,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,74; 42,63</t>
+          <t>32,87; 42,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36,55; 44,82</t>
+          <t>36,25; 44,35</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54,27; 63,03</t>
+          <t>54,54; 63,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36,3; 44,73</t>
+          <t>36,09; 44,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,71; 39,77</t>
+          <t>32,5; 39,38</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,49; 39,01</t>
+          <t>30,99; 39,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51,13; 59,47</t>
+          <t>50,93; 58,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>49,14; 57,29</t>
+          <t>48,87; 56,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47,39; 57,3</t>
+          <t>47,36; 55,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>45,08; 52,79</t>
+          <t>44,98; 52,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,58; 69,05</t>
+          <t>61,28; 69,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,41; 61,16</t>
+          <t>53,49; 61,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>62,09; 86,71</t>
+          <t>59,56; 66,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39,38; 44,73</t>
+          <t>39,46; 45,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57,43; 63,21</t>
+          <t>57,43; 63,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52,52; 58,07</t>
+          <t>52,71; 58,16</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>57,09; 78,84</t>
+          <t>54,55; 60,0</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>48,77; 56,19</t>
+          <t>48,34; 55,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>46,66; 54,28</t>
+          <t>46,52; 54,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50,13; 57,46</t>
+          <t>50,54; 57,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,52; 51,87</t>
+          <t>46,28; 54,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>54,76; 61,94</t>
+          <t>54,79; 62,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,52; 65,28</t>
+          <t>58,53; 65,43</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>53,14; 60,5</t>
+          <t>53,59; 60,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,97; 63,24</t>
+          <t>56,06; 62,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>52,68; 57,84</t>
+          <t>52,64; 57,99</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53,65; 58,99</t>
+          <t>53,87; 58,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52,76; 58,05</t>
+          <t>52,9; 57,85</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,26; 56,01</t>
+          <t>52,34; 57,45</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41,49; 45,0</t>
+          <t>41,5; 44,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47,31; 50,64</t>
+          <t>47,21; 50,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>46,51; 50,12</t>
+          <t>46,25; 49,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30,56; 42,29</t>
+          <t>40,03; 43,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>52,4; 56,04</t>
+          <t>52,49; 55,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>60,17; 63,38</t>
+          <t>60,19; 63,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,18; 56,77</t>
+          <t>52,98; 56,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>50,15; 62,25</t>
+          <t>49,42; 52,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>47,47; 49,9</t>
+          <t>47,5; 49,99</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54,39; 56,82</t>
+          <t>54,36; 56,72</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50,21; 52,73</t>
+          <t>50,28; 52,76</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41,94; 51,27</t>
+          <t>45,3; 47,61</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104871</t>
+          <t>107179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>102926</t>
+          <t>111362</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>207797</t>
+          <t>218541</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>98287; 128564</t>
+          <t>94973; 126542</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>146499; 182932</t>
+          <t>148414; 183820</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>147435; 182943</t>
+          <t>145714; 181620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85062; 124230</t>
+          <t>89952; 124423</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>118650; 153441</t>
+          <t>120442; 153780</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>198065; 229456</t>
+          <t>197152; 228574</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>179010; 211294</t>
+          <t>176503; 209655</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>89080; 117901</t>
+          <t>97455; 126691</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>225734; 273363</t>
+          <t>221610; 270289</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>354103; 402159</t>
+          <t>355243; 403986</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>336543; 381315</t>
+          <t>333677; 386243</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>185162; 234319</t>
+          <t>195597; 241055</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142847</t>
+          <t>147065</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>194193</t>
+          <t>204602</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>337040</t>
+          <t>351666</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>251902; 296146</t>
+          <t>253816; 299181</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>108206; 150558</t>
+          <t>108070; 148295</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89998; 126215</t>
+          <t>88500; 125621</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>117298; 171214</t>
+          <t>122490; 175504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>320626; 364253</t>
+          <t>324544; 365157</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>195345; 240743</t>
+          <t>192034; 242116</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>131606; 174526</t>
+          <t>132328; 172108</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>174341; 215320</t>
+          <t>186410; 224956</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>585875; 648448</t>
+          <t>585582; 647515</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>315881; 379294</t>
+          <t>315477; 378290</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>229320; 285717</t>
+          <t>230897; 287344</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>305548; 372395</t>
+          <t>317446; 385670</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83520</t>
+          <t>87520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>129422</t>
+          <t>133088</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>212942</t>
+          <t>220609</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>69188; 103449</t>
+          <t>70683; 103792</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>140067; 177119</t>
+          <t>139675; 175411</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>139000; 173422</t>
+          <t>138095; 172922</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70612; 99957</t>
+          <t>73418; 102870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>118394; 155407</t>
+          <t>119899; 155769</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>207125; 244189</t>
+          <t>208132; 242365</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>187338; 222503</t>
+          <t>187450; 222729</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>113783; 144472</t>
+          <t>117499; 148121</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>199572; 248076</t>
+          <t>199451; 248017</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>357979; 409743</t>
+          <t>359014; 411399</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>336164; 385729</t>
+          <t>335295; 387111</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>192313; 234516</t>
+          <t>201604; 243278</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98340</t>
+          <t>115925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>224166</t>
+          <t>172100</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>322506</t>
+          <t>288025</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129829; 167361</t>
+          <t>131177; 167655</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>220272; 259383</t>
+          <t>219844; 259354</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>143414; 182822</t>
+          <t>144666; 183217</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80733; 120029</t>
+          <t>94515; 138943</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>168786; 205756</t>
+          <t>169659; 206675</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>273504; 307641</t>
+          <t>271591; 308114</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>189842; 231103</t>
+          <t>188279; 228238</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>164430; 314072</t>
+          <t>151548; 192779</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>309828; 362832</t>
+          <t>312173; 365007</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>506012; 555130</t>
+          <t>500926; 557254</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>344531; 402183</t>
+          <t>345179; 401472</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>264951; 457321</t>
+          <t>259157; 317928</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136093</t>
+          <t>153757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>172816</t>
+          <t>187013</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>308909</t>
+          <t>340770</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>82367; 111106</t>
+          <t>84343; 113225</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>63217; 91340</t>
+          <t>64306; 92437</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>173351; 191828</t>
+          <t>172774; 191035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>125531; 145966</t>
+          <t>140731; 164552</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>110669; 139053</t>
+          <t>110984; 138790</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96054; 126520</t>
+          <t>96855; 125129</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>181304; 200115</t>
+          <t>182048; 200576</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>163381; 179497</t>
+          <t>177052; 194772</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202639; 242280</t>
+          <t>200252; 243244</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>165646; 209189</t>
+          <t>169113; 209822</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>359584; 386022</t>
+          <t>361382; 387489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>294601; 321481</t>
+          <t>324453; 355251</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92270</t>
+          <t>92584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>96734</t>
+          <t>99417</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>189004</t>
+          <t>192001</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>78172; 109732</t>
+          <t>78477; 109252</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>130088; 165772</t>
+          <t>132403; 163996</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76410; 107505</t>
+          <t>75712; 107051</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78591; 106841</t>
+          <t>77735; 105300</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>112979; 145455</t>
+          <t>111149; 145762</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>161569; 195322</t>
+          <t>161167; 192141</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>108670; 141912</t>
+          <t>107582; 142506</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>84162; 109593</t>
+          <t>86707; 112224</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>200634; 246048</t>
+          <t>198990; 243481</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>300652; 349178</t>
+          <t>302181; 350674</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>194637; 239882</t>
+          <t>193527; 239654</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>172123; 209295</t>
+          <t>173559; 210268</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>324896</t>
+          <t>367088</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>611516</t>
+          <t>485999</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>936412</t>
+          <t>853087</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>193679; 239938</t>
+          <t>190625; 240050</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>338897; 394137</t>
+          <t>337530; 390727</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>322642; 376137</t>
+          <t>320841; 372865</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>293769; 355192</t>
+          <t>338428; 399236</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>287707; 336946</t>
+          <t>287100; 336976</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>427250; 479121</t>
+          <t>425212; 479256</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>369187; 422823</t>
+          <t>369769; 423392</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>525784; 734326</t>
+          <t>458211; 511293</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>493496; 560623</t>
+          <t>494509; 565978</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>779124; 857495</t>
+          <t>779113; 855383</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>707831; 782686</t>
+          <t>710494; 783953</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>837413; 1156375</t>
+          <t>809491; 890398</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>347708</t>
+          <t>399864</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>428656</t>
+          <t>492607</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>776364</t>
+          <t>892471</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>362728; 417942</t>
+          <t>359543; 413107</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>363522; 422891</t>
+          <t>362469; 421052</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>390290; 447412</t>
+          <t>393463; 448836</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>153185; 480900</t>
+          <t>368556; 433898</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>429087; 485345</t>
+          <t>429282; 486040</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>482148; 537852</t>
+          <t>482220; 539060</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>439059; 499797</t>
+          <t>442779; 500499</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>407438; 452295</t>
+          <t>464414; 518587</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>804644; 883420</t>
+          <t>803926; 885688</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>859911; 945633</t>
+          <t>863454; 945196</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>846689; 931619</t>
+          <t>848854; 928399</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>447793; 919980</t>
+          <t>850357; 933478</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1330544</t>
+          <t>1470982</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1960429</t>
+          <t>1886188</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>3290973</t>
+          <t>3357170</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1359326; 1474346</t>
+          <t>1359732; 1472819</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1621155; 1735304</t>
+          <t>1617919; 1741217</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1578751; 1701411</t>
+          <t>1569963; 1684833</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1052445; 1456307</t>
+          <t>1407074; 1533452</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1770768; 1893868</t>
+          <t>1773654; 1890895</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2141157; 2255406</t>
+          <t>2141732; 2263726</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1884984; 2012236</t>
+          <t>1877885; 2002874</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>1827309; 2268094</t>
+          <t>1836258; 1940212</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3159395; 3321312</t>
+          <t>3161364; 3326987</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3799360; 3968661</t>
+          <t>3797016; 3961862</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3483912; 3659063</t>
+          <t>3488953; 3660935</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2972143; 3633796</t>
+          <t>3275867; 3442213</t>
         </is>
       </c>
     </row>
